--- a/ISRG_Model.xlsx
+++ b/ISRG_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8ADC064-0882-41A0-B9B7-742533274AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AF2979-20D0-481C-B232-A9FAF5BAEE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4665,9 +4665,6 @@
     <t>https://www.gurufocus.com/term/wacc/ISRG</t>
   </si>
   <si>
-    <t>9/12/25</t>
-  </si>
-  <si>
     <t>Master</t>
   </si>
   <si>
@@ -4681,6 +4678,9 @@
   </si>
   <si>
     <t>Q3'25</t>
+  </si>
+  <si>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -12022,7 +12022,7 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="44" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15">
@@ -12043,10 +12043,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="42">
-        <v>543.45000000000005</v>
+        <v>587.88</v>
       </c>
       <c r="D5" s="76" t="s">
-        <v>1513</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -12057,7 +12057,7 @@
         <v>354.49599999999998</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="C7" s="43">
         <f>C5*C6</f>
-        <v>192650.8512</v>
+        <v>208401.10848</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -12078,7 +12078,7 @@
         <v>4908.7999999999993</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -12089,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="C10" s="43">
         <f>C7-C8+C9</f>
-        <v>187742.05120000002</v>
+        <v>203492.30848000001</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="15">
@@ -12215,7 +12215,7 @@
     </row>
     <row r="22" spans="1:20">
       <c r="B22" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>8</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="33" spans="1:2" ht="15">
       <c r="B33" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15">
@@ -12297,9 +12297,6 @@
     <hyperlink ref="T17" r:id="rId8" xr:uid="{9F777450-107A-421F-B854-620668A2DD04}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D5" twoDigitTextYear="1"/>
-  </ignoredErrors>
   <drawing r:id="rId9"/>
 </worksheet>
 </file>
@@ -12957,39 +12954,39 @@
       </c>
       <c r="CN4" s="74">
         <f t="shared" ref="CN4:CV4" si="2">CM4*(1+CN9)</f>
-        <v>7101.9657000000007</v>
+        <v>7041.7795500000002</v>
       </c>
       <c r="CO4" s="74">
         <f t="shared" si="2"/>
-        <v>8309.2998690000004</v>
+        <v>8189.5896166500006</v>
       </c>
       <c r="CP4" s="74">
         <f t="shared" si="2"/>
-        <v>9618.0145983675011</v>
+        <v>9479.4499812723752</v>
       </c>
       <c r="CQ4" s="74">
         <f t="shared" si="2"/>
-        <v>11084.761824618547</v>
+        <v>10925.066103416413</v>
       </c>
       <c r="CR4" s="74">
         <f t="shared" si="2"/>
-        <v>12692.052289188236</v>
+        <v>12509.200688411793</v>
       </c>
       <c r="CS4" s="74">
         <f t="shared" si="2"/>
-        <v>14215.098563890826</v>
+        <v>14010.304771021209</v>
       </c>
       <c r="CT4" s="74">
         <f t="shared" si="2"/>
-        <v>15778.759405918818</v>
+        <v>15551.438295833543</v>
       </c>
       <c r="CU4" s="74">
         <f t="shared" si="2"/>
-        <v>17198.847752451511</v>
+        <v>16951.067742458563</v>
       </c>
       <c r="CV4" s="74">
         <f t="shared" si="2"/>
-        <v>18402.767095123119</v>
+        <v>18137.642484430664</v>
       </c>
     </row>
     <row r="5" spans="2:153">
@@ -13097,39 +13094,39 @@
       </c>
       <c r="CN5" s="74">
         <f t="shared" si="3"/>
-        <v>3058.1129999999994</v>
+        <v>3033.0464999999995</v>
       </c>
       <c r="CO5" s="74">
         <f t="shared" si="3"/>
-        <v>3639.154469999999</v>
+        <v>3563.8296374999995</v>
       </c>
       <c r="CP5" s="74">
         <f t="shared" si="3"/>
-        <v>4259.4378091444887</v>
+        <v>4171.2740771119843</v>
       </c>
       <c r="CQ5" s="74">
         <f t="shared" si="3"/>
-        <v>4940.9478586076066</v>
+        <v>4838.6779294499011</v>
       </c>
       <c r="CR5" s="74">
         <f t="shared" si="3"/>
-        <v>5607.9758195196337</v>
+        <v>5491.8994499256378</v>
       </c>
       <c r="CS5" s="74">
         <f t="shared" si="3"/>
-        <v>6224.8531596667935</v>
+        <v>6096.0083894174586</v>
       </c>
       <c r="CT5" s="74">
         <f t="shared" si="3"/>
-        <v>6862.90060853264</v>
+        <v>6720.8492493327485</v>
       </c>
       <c r="CU5" s="74">
         <f t="shared" si="3"/>
-        <v>7394.7754056939193</v>
+        <v>7241.7150661560363</v>
       </c>
       <c r="CV5" s="74">
         <f t="shared" si="3"/>
-        <v>7893.9227455782584</v>
+        <v>7730.5308331215683</v>
       </c>
     </row>
     <row r="6" spans="2:153">
@@ -13237,39 +13234,39 @@
       </c>
       <c r="CN6" s="74">
         <f t="shared" si="3"/>
-        <v>1819.8753299999996</v>
+        <v>1788.7663499999996</v>
       </c>
       <c r="CO6" s="74">
         <f t="shared" si="3"/>
-        <v>2092.8566294999996</v>
+        <v>2030.2498072499995</v>
       </c>
       <c r="CP6" s="74">
         <f t="shared" si="3"/>
-        <v>2364.9279913349992</v>
+        <v>2284.0310331562496</v>
       </c>
       <c r="CQ6" s="74">
         <f t="shared" si="3"/>
-        <v>2648.7193502951995</v>
+        <v>2558.1147571349998</v>
       </c>
       <c r="CR6" s="74">
         <f t="shared" si="3"/>
-        <v>2940.0784788276719</v>
+        <v>2839.5073804198501</v>
       </c>
       <c r="CS6" s="74">
         <f t="shared" si="3"/>
-        <v>3248.7867191045775</v>
+        <v>3137.6556553639343</v>
       </c>
       <c r="CT6" s="74">
         <f t="shared" si="3"/>
-        <v>3541.1775238239898</v>
+        <v>3420.0446643466885</v>
       </c>
       <c r="CU6" s="74">
         <f t="shared" si="3"/>
-        <v>3806.765838110789</v>
+        <v>3676.5480141726898</v>
       </c>
       <c r="CV6" s="74">
         <f t="shared" si="3"/>
-        <v>4054.2056175879902</v>
+        <v>3915.5236350939144</v>
       </c>
     </row>
     <row r="7" spans="2:153" s="2" customFormat="1" ht="15">
@@ -13400,39 +13397,39 @@
       </c>
       <c r="CN7" s="75">
         <f t="shared" ref="CN7:CV7" si="5">SUM(CN4:CN6)</f>
-        <v>11979.954029999999</v>
+        <v>11863.5924</v>
       </c>
       <c r="CO7" s="75">
         <f t="shared" si="5"/>
-        <v>14041.3109685</v>
+        <v>13783.6690614</v>
       </c>
       <c r="CP7" s="75">
         <f t="shared" si="5"/>
-        <v>16242.380398846988</v>
+        <v>15934.75509154061</v>
       </c>
       <c r="CQ7" s="75">
         <f t="shared" si="5"/>
-        <v>18674.429033521352</v>
+        <v>18321.858790001315</v>
       </c>
       <c r="CR7" s="75">
         <f t="shared" si="5"/>
-        <v>21240.106587535542</v>
+        <v>20840.607518757282</v>
       </c>
       <c r="CS7" s="75">
         <f t="shared" si="5"/>
-        <v>23688.738442662197</v>
+        <v>23243.9688158026</v>
       </c>
       <c r="CT7" s="75">
         <f t="shared" si="5"/>
-        <v>26182.837538275449</v>
+        <v>25692.332209512981</v>
       </c>
       <c r="CU7" s="75">
         <f t="shared" si="5"/>
-        <v>28400.388996256221</v>
+        <v>27869.330822787291</v>
       </c>
       <c r="CV7" s="75">
         <f t="shared" si="5"/>
-        <v>30350.895458289371</v>
+        <v>29783.696952646147</v>
       </c>
       <c r="CW7" s="34"/>
       <c r="CX7" s="34"/>
@@ -13593,10 +13590,10 @@
         <v>0.185</v>
       </c>
       <c r="CN9" s="72">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="CO9" s="72">
-        <v>0.17</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="CP9" s="72">
         <v>0.1575</v>
@@ -13721,10 +13718,10 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="CN10" s="72">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="CO10" s="72">
-        <v>0.19</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="CP10" s="72">
         <v>0.17044710364946125</v>
@@ -13849,13 +13846,13 @@
         <v>0.19</v>
       </c>
       <c r="CN11" s="72">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="CO11" s="72">
-        <v>0.15</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="CP11" s="72">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="CQ11" s="72">
         <v>0.12</v>
@@ -13984,39 +13981,39 @@
       </c>
       <c r="CN12" s="73">
         <f t="shared" ref="CN12:CV12" si="15">CN7/CM7-1</f>
-        <v>0.18840332440737817</v>
+        <v>0.17686032953618169</v>
       </c>
       <c r="CO12" s="73">
         <f t="shared" si="15"/>
-        <v>0.17206718267348831</v>
+        <v>0.16184614210110593</v>
       </c>
       <c r="CP12" s="73">
         <f t="shared" si="15"/>
-        <v>0.15675668997608727</v>
+        <v>0.15606048146966511</v>
       </c>
       <c r="CQ12" s="73">
         <f t="shared" si="15"/>
-        <v>0.14973474176525325</v>
+        <v>0.14980485641275809</v>
       </c>
       <c r="CR12" s="73">
         <f t="shared" si="15"/>
-        <v>0.13738987946612435</v>
+        <v>0.13747233605634546</v>
       </c>
       <c r="CS12" s="73">
         <f t="shared" si="15"/>
-        <v>0.1152834071258193</v>
+        <v>0.11532107664722391</v>
       </c>
       <c r="CT12" s="73">
         <f t="shared" si="15"/>
-        <v>0.10528627776654864</v>
+        <v>0.10533327647754542</v>
       </c>
       <c r="CU12" s="73">
         <f t="shared" si="15"/>
-        <v>8.4694848476183582E-2</v>
+        <v>8.4733398101875856E-2</v>
       </c>
       <c r="CV12" s="73">
         <f t="shared" si="15"/>
-        <v>6.8678864303241438E-2</v>
+        <v>6.8690782065480294E-2</v>
       </c>
       <c r="CW12" s="34"/>
       <c r="CX12" s="34"/>
@@ -14557,39 +14554,39 @@
       </c>
       <c r="CN18" s="75">
         <f t="shared" ref="CN18:CV18" si="28">CN7</f>
-        <v>11979.954029999999</v>
+        <v>11863.5924</v>
       </c>
       <c r="CO18" s="75">
         <f t="shared" si="28"/>
-        <v>14041.3109685</v>
+        <v>13783.6690614</v>
       </c>
       <c r="CP18" s="75">
         <f t="shared" si="28"/>
-        <v>16242.380398846988</v>
+        <v>15934.75509154061</v>
       </c>
       <c r="CQ18" s="75">
         <f t="shared" si="28"/>
-        <v>18674.429033521352</v>
+        <v>18321.858790001315</v>
       </c>
       <c r="CR18" s="75">
         <f t="shared" si="28"/>
-        <v>21240.106587535542</v>
+        <v>20840.607518757282</v>
       </c>
       <c r="CS18" s="75">
         <f t="shared" si="28"/>
-        <v>23688.738442662197</v>
+        <v>23243.9688158026</v>
       </c>
       <c r="CT18" s="75">
         <f t="shared" si="28"/>
-        <v>26182.837538275449</v>
+        <v>25692.332209512981</v>
       </c>
       <c r="CU18" s="75">
         <f t="shared" si="28"/>
-        <v>28400.388996256221</v>
+        <v>27869.330822787291</v>
       </c>
       <c r="CV18" s="75">
         <f t="shared" si="28"/>
-        <v>30350.895458289371</v>
+        <v>29783.696952646147</v>
       </c>
       <c r="CW18" s="34"/>
       <c r="CX18" s="34"/>
@@ -14748,39 +14745,39 @@
       </c>
       <c r="CN19" s="74">
         <f t="shared" ref="CN19:CV19" si="29">CN18*(1-CN33)</f>
-        <v>3893.485059749999</v>
+        <v>3855.6675299999993</v>
       </c>
       <c r="CO19" s="74">
         <f t="shared" si="29"/>
-        <v>4528.3227873412498</v>
+        <v>4445.2332723014997</v>
       </c>
       <c r="CP19" s="74">
         <f t="shared" si="29"/>
-        <v>5197.561727631035</v>
+        <v>5099.1216292929948</v>
       </c>
       <c r="CQ19" s="74">
         <f t="shared" si="29"/>
-        <v>5882.4451455592252</v>
+        <v>5771.3855188504131</v>
       </c>
       <c r="CR19" s="74">
         <f t="shared" si="29"/>
-        <v>6584.4330421360191</v>
+        <v>6460.5883308147586</v>
       </c>
       <c r="CS19" s="74">
         <f t="shared" si="29"/>
-        <v>7225.0652250119711</v>
+        <v>7089.4104888197944</v>
       </c>
       <c r="CT19" s="74">
         <f t="shared" si="29"/>
-        <v>7854.8512614826359</v>
+        <v>7707.6996628538955</v>
       </c>
       <c r="CU19" s="74">
         <f t="shared" si="29"/>
-        <v>8236.1128089143058</v>
+        <v>8082.1059386083152</v>
       </c>
       <c r="CV19" s="74">
         <f t="shared" si="29"/>
-        <v>8801.7596829039194</v>
+        <v>8637.2721162673843</v>
       </c>
     </row>
     <row r="20" spans="2:152">
@@ -14905,39 +14902,39 @@
       </c>
       <c r="CN20" s="74">
         <f t="shared" ref="CN20:CV20" si="32">CN18*CN33</f>
-        <v>8086.46897025</v>
+        <v>8007.9248699999998</v>
       </c>
       <c r="CO20" s="74">
         <f t="shared" si="32"/>
-        <v>9512.9881811587493</v>
+        <v>9338.4357890984993</v>
       </c>
       <c r="CP20" s="74">
         <f t="shared" si="32"/>
-        <v>11044.818671215953</v>
+        <v>10835.633462247615</v>
       </c>
       <c r="CQ20" s="74">
         <f t="shared" si="32"/>
-        <v>12791.983887962127</v>
+        <v>12550.473271150902</v>
       </c>
       <c r="CR20" s="74">
         <f t="shared" si="32"/>
-        <v>14655.673545399522</v>
+        <v>14380.019187942524</v>
       </c>
       <c r="CS20" s="74">
         <f t="shared" si="32"/>
-        <v>16463.673217650226</v>
+        <v>16154.558326982806</v>
       </c>
       <c r="CT20" s="74">
         <f t="shared" si="32"/>
-        <v>18327.986276792813</v>
+        <v>17984.632546659086</v>
       </c>
       <c r="CU20" s="74">
         <f t="shared" si="32"/>
-        <v>20164.276187341915</v>
+        <v>19787.224884178977</v>
       </c>
       <c r="CV20" s="74">
         <f t="shared" si="32"/>
-        <v>21549.135775385454</v>
+        <v>21146.424836378763</v>
       </c>
     </row>
     <row r="21" spans="2:152">
@@ -15044,39 +15041,39 @@
       </c>
       <c r="CN21" s="74">
         <f t="shared" ref="CN21:CV21" si="33">CN18*CN34</f>
-        <v>2707.46961078</v>
+        <v>2681.1718824</v>
       </c>
       <c r="CO21" s="74">
         <f t="shared" si="33"/>
-        <v>3117.1710350070002</v>
+        <v>3059.9745316307999</v>
       </c>
       <c r="CP21" s="74">
         <f t="shared" si="33"/>
-        <v>3573.3236877463373</v>
+        <v>3505.6461201389343</v>
       </c>
       <c r="CQ21" s="74">
         <f t="shared" si="33"/>
-        <v>4071.0255293076548</v>
+        <v>3994.1652162202868</v>
       </c>
       <c r="CR21" s="74">
         <f t="shared" si="33"/>
-        <v>4587.8630229076771</v>
+        <v>4501.5712240515732</v>
       </c>
       <c r="CS21" s="74">
         <f t="shared" si="33"/>
-        <v>5069.3900267297104</v>
+        <v>4974.2093265817566</v>
       </c>
       <c r="CT21" s="74">
         <f t="shared" si="33"/>
-        <v>5550.7615581143955</v>
+        <v>5446.774428416752</v>
       </c>
       <c r="CU21" s="74">
         <f t="shared" si="33"/>
-        <v>5964.0816892138064</v>
+        <v>5852.5594727853313</v>
       </c>
       <c r="CV21" s="74">
         <f t="shared" si="33"/>
-        <v>6373.688046240768</v>
+        <v>6254.5763600556911</v>
       </c>
     </row>
     <row r="22" spans="2:152">
@@ -15183,39 +15180,39 @@
       </c>
       <c r="CN22" s="74">
         <f t="shared" ref="CN22:CV22" si="34">CN18*CN35</f>
-        <v>1587.343908975</v>
+        <v>1571.9259930000001</v>
       </c>
       <c r="CO22" s="74">
         <f t="shared" si="34"/>
-        <v>1825.370425905</v>
+        <v>1791.876977982</v>
       </c>
       <c r="CP22" s="74">
         <f t="shared" si="34"/>
-        <v>2095.2670714512615</v>
+        <v>2055.5834068087388</v>
       </c>
       <c r="CQ22" s="74">
         <f t="shared" si="34"/>
-        <v>2390.3269162907332</v>
+        <v>2345.1979251201683</v>
       </c>
       <c r="CR22" s="74">
         <f t="shared" si="34"/>
-        <v>2697.4935366170139</v>
+        <v>2646.7571548821747</v>
       </c>
       <c r="CS22" s="74">
         <f t="shared" si="34"/>
-        <v>2984.781043775437</v>
+        <v>2928.7400707911274</v>
       </c>
       <c r="CT22" s="74">
         <f t="shared" si="34"/>
-        <v>3272.8546922844312</v>
+        <v>3211.5415261891226</v>
       </c>
       <c r="CU22" s="74">
         <f t="shared" si="34"/>
-        <v>3550.0486245320276</v>
+        <v>3483.6663528484114</v>
       </c>
       <c r="CV22" s="74">
         <f t="shared" si="34"/>
-        <v>3793.8619322861714</v>
+        <v>3722.9621190807684</v>
       </c>
     </row>
     <row r="23" spans="2:152">
@@ -15340,39 +15337,39 @@
       </c>
       <c r="CN23" s="74">
         <f t="shared" ref="CN23:CV23" si="37">CN20-SUM(CN21:CN22)</f>
-        <v>3791.655450495</v>
+        <v>3754.8269946</v>
       </c>
       <c r="CO23" s="74">
         <f t="shared" si="37"/>
-        <v>4570.4467202467495</v>
+        <v>4486.5842794856999</v>
       </c>
       <c r="CP23" s="74">
         <f t="shared" si="37"/>
-        <v>5376.2279120183539</v>
+        <v>5274.4039352999425</v>
       </c>
       <c r="CQ23" s="74">
         <f t="shared" si="37"/>
-        <v>6330.6314423637396</v>
+        <v>6211.1101298104477</v>
       </c>
       <c r="CR23" s="74">
         <f t="shared" si="37"/>
-        <v>7370.3169858748315</v>
+        <v>7231.6908090087763</v>
       </c>
       <c r="CS23" s="74">
         <f t="shared" si="37"/>
-        <v>8409.5021471450782</v>
+        <v>8251.6089296099217</v>
       </c>
       <c r="CT23" s="74">
         <f t="shared" si="37"/>
-        <v>9504.3700263939863</v>
+        <v>9326.3165920532119</v>
       </c>
       <c r="CU23" s="74">
         <f t="shared" si="37"/>
-        <v>10650.14587359608</v>
+        <v>10450.999058545234</v>
       </c>
       <c r="CV23" s="74">
         <f t="shared" si="37"/>
-        <v>11381.585796858515</v>
+        <v>11168.886357242303</v>
       </c>
     </row>
     <row r="24" spans="2:152">
@@ -15475,43 +15472,43 @@
       </c>
       <c r="CM24" s="74">
         <f>CL40*$CV$42</f>
-        <v>451.09650000000005</v>
+        <v>466.30200000000002</v>
       </c>
       <c r="CN24" s="74">
         <f t="shared" ref="CN24:CV24" si="38">CM40*$CV$42</f>
-        <v>1156.234882575</v>
+        <v>1198.2866853</v>
       </c>
       <c r="CO24" s="74">
         <f t="shared" si="38"/>
-        <v>2080.9955858257831</v>
+        <v>2155.2282482566798</v>
       </c>
       <c r="CP24" s="74">
         <f t="shared" si="38"/>
-        <v>3324.1501528307394</v>
+        <v>3438.4264286165076</v>
       </c>
       <c r="CQ24" s="74">
         <f t="shared" si="38"/>
-        <v>4950.2508131510358</v>
+        <v>5121.7452549251648</v>
       </c>
       <c r="CR24" s="74">
         <f t="shared" si="38"/>
-        <v>7058.6477067067462</v>
+        <v>7311.2529152560855</v>
       </c>
       <c r="CS24" s="74">
         <f t="shared" si="38"/>
-        <v>9755.4212077502434</v>
+        <v>10120.949642784057</v>
       </c>
       <c r="CT24" s="74">
         <f t="shared" si="38"/>
-        <v>13150.445382780177</v>
+        <v>13670.527958970573</v>
       </c>
       <c r="CU24" s="74">
         <f t="shared" si="38"/>
-        <v>17384.630382754829</v>
+        <v>18113.518326228368</v>
       </c>
       <c r="CV24" s="74">
         <f t="shared" si="38"/>
-        <v>22624.330065066813</v>
+        <v>23632.183084966629</v>
       </c>
     </row>
     <row r="25" spans="2:152">
@@ -15632,43 +15629,43 @@
       </c>
       <c r="CM25" s="74">
         <f>CM23+CM24</f>
-        <v>3601.3196250000001</v>
+        <v>3616.5251250000001</v>
       </c>
       <c r="CN25" s="74">
         <f t="shared" ref="CN25:CV25" si="41">CN23+CN24</f>
-        <v>4947.8903330699995</v>
+        <v>4953.1136798999996</v>
       </c>
       <c r="CO25" s="74">
         <f t="shared" si="41"/>
-        <v>6651.442306072533</v>
+        <v>6641.8125277423796</v>
       </c>
       <c r="CP25" s="74">
         <f t="shared" si="41"/>
-        <v>8700.3780648490938</v>
+        <v>8712.8303639164496</v>
       </c>
       <c r="CQ25" s="74">
         <f t="shared" si="41"/>
-        <v>11280.882255514774</v>
+        <v>11332.855384735612</v>
       </c>
       <c r="CR25" s="74">
         <f t="shared" si="41"/>
-        <v>14428.964692581578</v>
+        <v>14542.943724264862</v>
       </c>
       <c r="CS25" s="74">
         <f t="shared" si="41"/>
-        <v>18164.92335489532</v>
+        <v>18372.55857239398</v>
       </c>
       <c r="CT25" s="74">
         <f t="shared" si="41"/>
-        <v>22654.815409174164</v>
+        <v>22996.844551023787</v>
       </c>
       <c r="CU25" s="74">
         <f t="shared" si="41"/>
-        <v>28034.77625635091</v>
+        <v>28564.5173847736</v>
       </c>
       <c r="CV25" s="74">
         <f t="shared" si="41"/>
-        <v>34005.915861925328</v>
+        <v>34801.069442208929</v>
       </c>
     </row>
     <row r="26" spans="2:152">
@@ -15771,43 +15768,43 @@
       </c>
       <c r="CM26" s="74">
         <f>CM25*CM37</f>
-        <v>432.15835499999997</v>
+        <v>433.98301500000002</v>
       </c>
       <c r="CN26" s="74">
         <f t="shared" ref="CN26:CV26" si="42">CN25*CN37</f>
-        <v>791.66245329119999</v>
+        <v>792.49818878399992</v>
       </c>
       <c r="CO26" s="74">
         <f t="shared" si="42"/>
-        <v>1064.2307689716054</v>
+        <v>1062.6900044387808</v>
       </c>
       <c r="CP26" s="74">
         <f t="shared" si="42"/>
-        <v>1392.0604903758551</v>
+        <v>1394.052858226632</v>
       </c>
       <c r="CQ26" s="74">
         <f t="shared" si="42"/>
-        <v>1804.9411608823639</v>
+        <v>1813.2568615576981</v>
       </c>
       <c r="CR26" s="74">
         <f t="shared" si="42"/>
-        <v>2308.6343508130526</v>
+        <v>2326.8709958823779</v>
       </c>
       <c r="CS26" s="74">
         <f t="shared" si="42"/>
-        <v>2906.3877367832511</v>
+        <v>2939.609371583037</v>
       </c>
       <c r="CT26" s="74">
         <f t="shared" si="42"/>
-        <v>3624.7704654678664</v>
+        <v>3679.4951281638059</v>
       </c>
       <c r="CU26" s="74">
         <f t="shared" si="42"/>
-        <v>4485.5642010161455</v>
+        <v>4570.3227815637765</v>
       </c>
       <c r="CV26" s="74">
         <f t="shared" si="42"/>
-        <v>5440.946537908053</v>
+        <v>5568.1711107534284</v>
       </c>
     </row>
     <row r="27" spans="2:152" s="2" customFormat="1" ht="15">
@@ -15933,243 +15930,243 @@
       </c>
       <c r="CM27" s="75">
         <f>CM25-CM26</f>
-        <v>3169.1612700000001</v>
+        <v>3182.5421100000003</v>
       </c>
       <c r="CN27" s="75">
         <f t="shared" ref="CN27:CV27" si="45">CN25-CN26</f>
-        <v>4156.2278797787994</v>
+        <v>4160.6154911159992</v>
       </c>
       <c r="CO27" s="75">
         <f t="shared" si="45"/>
-        <v>5587.2115371009277</v>
+        <v>5579.1225233035984</v>
       </c>
       <c r="CP27" s="75">
         <f t="shared" si="45"/>
-        <v>7308.3175744732389</v>
+        <v>7318.7775056898172</v>
       </c>
       <c r="CQ27" s="75">
         <f t="shared" si="45"/>
-        <v>9475.9410946324097</v>
+        <v>9519.5985231779141</v>
       </c>
       <c r="CR27" s="75">
         <f t="shared" si="45"/>
-        <v>12120.330341768526</v>
+        <v>12216.072728382484</v>
       </c>
       <c r="CS27" s="75">
         <f t="shared" si="45"/>
-        <v>15258.53561811207</v>
+        <v>15432.949200810943</v>
       </c>
       <c r="CT27" s="75">
         <f t="shared" si="45"/>
-        <v>19030.044943706296</v>
+        <v>19317.349422859981</v>
       </c>
       <c r="CU27" s="75">
         <f t="shared" si="45"/>
-        <v>23549.212055334763</v>
+        <v>23994.194603209824</v>
       </c>
       <c r="CV27" s="75">
         <f t="shared" si="45"/>
-        <v>28564.969324017275</v>
+        <v>29232.898331455501</v>
       </c>
       <c r="CW27" s="75">
         <f>CV27*(1+$CV$43)</f>
-        <v>29279.093557117703</v>
+        <v>29963.720789741885</v>
       </c>
       <c r="CX27" s="75">
         <f t="shared" ref="CX27:ET27" si="46">CW27*(1+$CV$43)</f>
-        <v>30011.070896045643</v>
+        <v>30712.813809485429</v>
       </c>
       <c r="CY27" s="75">
         <f t="shared" si="46"/>
-        <v>30761.347668446782</v>
+        <v>31480.634154722564</v>
       </c>
       <c r="CZ27" s="75">
         <f t="shared" si="46"/>
-        <v>31530.38136015795</v>
+        <v>32267.650008590626</v>
       </c>
       <c r="DA27" s="75">
         <f t="shared" si="46"/>
-        <v>32318.640894161894</v>
+        <v>33074.341258805391</v>
       </c>
       <c r="DB27" s="75">
         <f t="shared" si="46"/>
-        <v>33126.606916515935</v>
+        <v>33901.199790275525</v>
       </c>
       <c r="DC27" s="75">
         <f t="shared" si="46"/>
-        <v>33954.772089428829</v>
+        <v>34748.72978503241</v>
       </c>
       <c r="DD27" s="75">
         <f t="shared" si="46"/>
-        <v>34803.641391664547</v>
+        <v>35617.448029658219</v>
       </c>
       <c r="DE27" s="75">
         <f t="shared" si="46"/>
-        <v>35673.732426456161</v>
+        <v>36507.884230399672</v>
       </c>
       <c r="DF27" s="75">
         <f t="shared" si="46"/>
-        <v>36565.575737117564</v>
+        <v>37420.581336159659</v>
       </c>
       <c r="DG27" s="75">
         <f t="shared" si="46"/>
-        <v>37479.715130545497</v>
+        <v>38356.095869563651</v>
       </c>
       <c r="DH27" s="75">
         <f t="shared" si="46"/>
-        <v>38416.708008809132</v>
+        <v>39314.99826630274</v>
       </c>
       <c r="DI27" s="75">
         <f t="shared" si="46"/>
-        <v>39377.125709029358</v>
+        <v>40297.873222960305</v>
       </c>
       <c r="DJ27" s="75">
         <f t="shared" si="46"/>
-        <v>40361.553851755089</v>
+        <v>41305.320053534306</v>
       </c>
       <c r="DK27" s="75">
         <f t="shared" si="46"/>
-        <v>41370.59269804896</v>
+        <v>42337.953054872662</v>
       </c>
       <c r="DL27" s="75">
         <f t="shared" si="46"/>
-        <v>42404.857515500182</v>
+        <v>43396.401881244477</v>
       </c>
       <c r="DM27" s="75">
         <f t="shared" si="46"/>
-        <v>43464.978953387683</v>
+        <v>44481.311928275587</v>
       </c>
       <c r="DN27" s="75">
         <f t="shared" si="46"/>
-        <v>44551.60342722237</v>
+        <v>45593.344726482472</v>
       </c>
       <c r="DO27" s="75">
         <f t="shared" si="46"/>
-        <v>45665.393512902927</v>
+        <v>46733.178344644526</v>
       </c>
       <c r="DP27" s="75">
         <f t="shared" si="46"/>
-        <v>46807.028350725494</v>
+        <v>47901.507803260632</v>
       </c>
       <c r="DQ27" s="75">
         <f t="shared" si="46"/>
-        <v>47977.204059493626</v>
+        <v>49099.045498342144</v>
       </c>
       <c r="DR27" s="75">
         <f t="shared" si="46"/>
-        <v>49176.634160980961</v>
+        <v>50326.521635800695</v>
       </c>
       <c r="DS27" s="75">
         <f t="shared" si="46"/>
-        <v>50406.05001500548</v>
+        <v>51584.68467669571</v>
       </c>
       <c r="DT27" s="75">
         <f t="shared" si="46"/>
-        <v>51666.201265380609</v>
+        <v>52874.3017936131</v>
       </c>
       <c r="DU27" s="75">
         <f t="shared" si="46"/>
-        <v>52957.856297015118</v>
+        <v>54196.159338453421</v>
       </c>
       <c r="DV27" s="75">
         <f t="shared" si="46"/>
-        <v>54281.802704440488</v>
+        <v>55551.063321914749</v>
       </c>
       <c r="DW27" s="75">
         <f t="shared" si="46"/>
-        <v>55638.847772051493</v>
+        <v>56939.83990496261</v>
       </c>
       <c r="DX27" s="75">
         <f t="shared" si="46"/>
-        <v>57029.818966352774</v>
+        <v>58363.335902586667</v>
       </c>
       <c r="DY27" s="75">
         <f t="shared" si="46"/>
-        <v>58455.564440511589</v>
+        <v>59822.419300151327</v>
       </c>
       <c r="DZ27" s="75">
         <f t="shared" si="46"/>
-        <v>59916.953551524377</v>
+        <v>61317.979782655108</v>
       </c>
       <c r="EA27" s="75">
         <f t="shared" si="46"/>
-        <v>61414.877390312482</v>
+        <v>62850.929277221483</v>
       </c>
       <c r="EB27" s="75">
         <f t="shared" si="46"/>
-        <v>62950.24932507029</v>
+        <v>64422.202509152012</v>
       </c>
       <c r="EC27" s="75">
         <f t="shared" si="46"/>
-        <v>64524.005558197045</v>
+        <v>66032.757571880808</v>
       </c>
       <c r="ED27" s="75">
         <f t="shared" si="46"/>
-        <v>66137.105697151972</v>
+        <v>67683.576511177816</v>
       </c>
       <c r="EE27" s="75">
         <f t="shared" si="46"/>
-        <v>67790.533339580768</v>
+        <v>69375.665923957262</v>
       </c>
       <c r="EF27" s="75">
         <f t="shared" si="46"/>
-        <v>69485.296673070276</v>
+        <v>71110.05757205619</v>
       </c>
       <c r="EG27" s="75">
         <f t="shared" si="46"/>
-        <v>71222.429089897021</v>
+        <v>72887.809011357589</v>
       </c>
       <c r="EH27" s="75">
         <f t="shared" si="46"/>
-        <v>73002.989817144437</v>
+        <v>74710.004236641529</v>
       </c>
       <c r="EI27" s="75">
         <f t="shared" si="46"/>
-        <v>74828.064562573039</v>
+        <v>76577.754342557557</v>
       </c>
       <c r="EJ27" s="75">
         <f t="shared" si="46"/>
-        <v>76698.766176637364</v>
+        <v>78492.198201121486</v>
       </c>
       <c r="EK27" s="75">
         <f t="shared" si="46"/>
-        <v>78616.235331053293</v>
+        <v>80454.503156149513</v>
       </c>
       <c r="EL27" s="75">
         <f t="shared" si="46"/>
-        <v>80581.641214329618</v>
+        <v>82465.865735053245</v>
       </c>
       <c r="EM27" s="75">
         <f t="shared" si="46"/>
-        <v>82596.18224468785</v>
+        <v>84527.512378429572</v>
       </c>
       <c r="EN27" s="75">
         <f t="shared" si="46"/>
-        <v>84661.086800805046</v>
+        <v>86640.70018789031</v>
       </c>
       <c r="EO27" s="75">
         <f t="shared" si="46"/>
-        <v>86777.613970825158</v>
+        <v>88806.717692587554</v>
       </c>
       <c r="EP27" s="75">
         <f t="shared" si="46"/>
-        <v>88947.054320095776</v>
+        <v>91026.885634902239</v>
       </c>
       <c r="EQ27" s="75">
         <f t="shared" si="46"/>
-        <v>91170.73067809816</v>
+        <v>93302.557775774781</v>
       </c>
       <c r="ER27" s="75">
         <f t="shared" si="46"/>
-        <v>93449.998945050611</v>
+        <v>95635.121720169147</v>
       </c>
       <c r="ES27" s="75">
         <f t="shared" si="46"/>
-        <v>95786.248918676865</v>
+        <v>98025.999763173371</v>
       </c>
       <c r="ET27" s="75">
         <f t="shared" si="46"/>
-        <v>98180.905141643772</v>
+        <v>100476.6497572527</v>
       </c>
       <c r="EU27" s="34"/>
       <c r="EV27" s="34"/>
@@ -17192,11 +17189,11 @@
       </c>
       <c r="CO36" s="72">
         <f t="shared" si="58"/>
-        <v>0.32549999999999996</v>
+        <v>0.32550000000000001</v>
       </c>
       <c r="CP36" s="72">
         <f t="shared" si="58"/>
-        <v>0.33100000000000007</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="CQ36" s="72">
         <f t="shared" si="58"/>
@@ -17204,7 +17201,7 @@
       </c>
       <c r="CR36" s="72">
         <f t="shared" si="58"/>
-        <v>0.34699999999999992</v>
+        <v>0.34699999999999998</v>
       </c>
       <c r="CS36" s="72">
         <f t="shared" si="58"/>
@@ -17212,15 +17209,15 @@
       </c>
       <c r="CT36" s="72">
         <f t="shared" si="58"/>
-        <v>0.36299999999999993</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="CU36" s="72">
         <f t="shared" si="58"/>
-        <v>0.37499999999999994</v>
+        <v>0.375</v>
       </c>
       <c r="CV36" s="72">
         <f t="shared" si="58"/>
-        <v>0.37500000000000006</v>
+        <v>0.37499999999999994</v>
       </c>
     </row>
     <row r="37" spans="2:102">
@@ -17488,43 +17485,43 @@
       </c>
       <c r="CM38" s="72">
         <f t="shared" si="63"/>
-        <v>0.31437865115506702</v>
+        <v>0.31570602141872095</v>
       </c>
       <c r="CN38" s="72">
         <f t="shared" ref="CN38:CV38" si="64">CN27/CN18</f>
-        <v>0.34693187213998011</v>
+        <v>0.35070452109565053</v>
       </c>
       <c r="CO38" s="72">
         <f t="shared" si="64"/>
-        <v>0.39791238507822863</v>
+        <v>0.40476323818071486</v>
       </c>
       <c r="CP38" s="72">
         <f t="shared" si="64"/>
-        <v>0.44995360255151029</v>
+        <v>0.45929651655425729</v>
       </c>
       <c r="CQ38" s="72">
         <f t="shared" si="64"/>
-        <v>0.5074286918021812</v>
+        <v>0.51957602295095684</v>
       </c>
       <c r="CR38" s="72">
         <f t="shared" si="64"/>
-        <v>0.57063415815818797</v>
+        <v>0.5861668244261875</v>
       </c>
       <c r="CS38" s="72">
         <f t="shared" si="64"/>
-        <v>0.64412613846215772</v>
+        <v>0.66395499508322897</v>
       </c>
       <c r="CT38" s="72">
         <f t="shared" si="64"/>
-        <v>0.72681369679230434</v>
+        <v>0.75187216424468606</v>
       </c>
       <c r="CU38" s="72">
         <f t="shared" si="64"/>
-        <v>0.82918625017562453</v>
+        <v>0.86095338118384346</v>
       </c>
       <c r="CV38" s="72">
         <f t="shared" si="64"/>
-        <v>0.94115738243286895</v>
+        <v>0.98150670744245161</v>
       </c>
     </row>
     <row r="39" spans="2:102">
@@ -17614,43 +17611,43 @@
       </c>
       <c r="CM40" s="74">
         <f>CL40+CM27</f>
-        <v>5196.5612700000001</v>
+        <v>5209.94211</v>
       </c>
       <c r="CN40" s="74">
         <f t="shared" ref="CN40:CV40" si="69">CM40+CN27</f>
-        <v>9352.7891497788005</v>
+        <v>9370.5576011159992</v>
       </c>
       <c r="CO40" s="74">
         <f t="shared" si="69"/>
-        <v>14940.000686879728</v>
+        <v>14949.680124419598</v>
       </c>
       <c r="CP40" s="74">
         <f t="shared" si="69"/>
-        <v>22248.318261352968</v>
+        <v>22268.457630109413</v>
       </c>
       <c r="CQ40" s="74">
         <f t="shared" si="69"/>
-        <v>31724.259355985378</v>
+        <v>31788.056153287325</v>
       </c>
       <c r="CR40" s="74">
         <f t="shared" si="69"/>
-        <v>43844.589697753901</v>
+        <v>44004.128881669807</v>
       </c>
       <c r="CS40" s="74">
         <f t="shared" si="69"/>
-        <v>59103.125315865967</v>
+        <v>59437.078082480752</v>
       </c>
       <c r="CT40" s="74">
         <f t="shared" si="69"/>
-        <v>78133.17025957226</v>
+        <v>78754.427505340733</v>
       </c>
       <c r="CU40" s="74">
         <f t="shared" si="69"/>
-        <v>101682.38231490702</v>
+        <v>102748.62210855055</v>
       </c>
       <c r="CV40" s="74">
         <f t="shared" si="69"/>
-        <v>130247.3516389243</v>
+        <v>131981.52044000605</v>
       </c>
     </row>
     <row r="41" spans="2:102">
@@ -17833,7 +17830,7 @@
         <v>1497</v>
       </c>
       <c r="CV42" s="63">
-        <v>0.2225</v>
+        <v>0.23</v>
       </c>
       <c r="CW42" s="60"/>
       <c r="CX42" s="60"/>
@@ -18047,7 +18044,7 @@
         <v>1500</v>
       </c>
       <c r="CV44" s="63">
-        <v>3.9899999999999998E-2</v>
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="CW44" s="60"/>
       <c r="CX44" s="60"/>
@@ -18148,7 +18145,7 @@
       </c>
       <c r="CV45" s="63">
         <f>7.75%-CV44</f>
-        <v>3.7600000000000001E-2</v>
+        <v>3.6400000000000002E-2</v>
       </c>
       <c r="CW45" s="60"/>
       <c r="CX45" s="60"/>
@@ -18344,7 +18341,7 @@
       </c>
       <c r="CV47" s="63">
         <f>+CV44+(CV45*CV46)</f>
-        <v>0.10306799999999999</v>
+        <v>0.102252</v>
       </c>
       <c r="CW47" s="60"/>
       <c r="CX47" s="60"/>
@@ -18579,7 +18576,7 @@
       </c>
       <c r="CV49" s="64">
         <f>NPV(CV47,CM27:ET27)</f>
-        <v>201772.69992827671</v>
+        <v>208443.8598689932</v>
       </c>
       <c r="CW49" s="60"/>
       <c r="CX49" s="60"/>
@@ -18768,7 +18765,7 @@
       </c>
       <c r="CV51" s="67">
         <f>CV49/CV50</f>
-        <v>569.18188055232417</v>
+        <v>588.00059766257789</v>
       </c>
       <c r="CW51" s="69"/>
       <c r="CX51" s="60"/>
@@ -18866,7 +18863,7 @@
       </c>
       <c r="CV52" s="67">
         <f>Main!C5</f>
-        <v>543.45000000000005</v>
+        <v>587.88</v>
       </c>
       <c r="CW52" s="70"/>
       <c r="CX52" s="71"/>
@@ -18964,7 +18961,7 @@
       </c>
       <c r="CV53" s="63">
         <f>CV51/CV52-1</f>
-        <v>4.7349122370639707E-2</v>
+        <v>2.0513993090065519E-4</v>
       </c>
       <c r="CW53" s="69" t="str">
         <f>IF(CV53&gt;0,"Upside","Downside")</f>
@@ -21106,7 +21103,7 @@
         <v>166</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="CA2" s="1">
         <v>0</v>

--- a/ISRG_Model.xlsx
+++ b/ISRG_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AF2979-20D0-481C-B232-A9FAF5BAEE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C8F2E3-AF0A-456B-8D7E-D982E9784708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-780" yWindow="1200" windowWidth="29010" windowHeight="15480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
